--- a/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, Diego se lève. Papa l'appelle. Ils vont dans la salle de bain. Diego prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Diego rit un peu. Il range la brosse. Le soir, maman l'appelle. C'est pareil. Diego prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. Matin et soir. Diego dit : matin et soir. Maman dit : oui, avec un adulte. Les dents sont propres. Diego pose la brosse.</t>
+          <t>Le matin, Diego se lève. Papa l'appelle. Ils vont dans la salle de bain. Diego prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Diego rit un peu. Il range la brosse. Le soir, maman l'appelle. C'est pareil. Diego prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. Matin et soir. Matin et soir. Oui, avec un adulte. Les dents sont propres. Diego pose la brosse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Diego se lève. Papa l'appelle. Ils vont dans la salle de bain. Diego prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Diego rit un peu. Il range la brosse. Le soir, maman l'appelle. C'est pareil. Diego prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. Matin et soir.
+enfant-m|Matin et soir.
+maman|Oui, avec un adulte.
+narrateur|Les dents sont propres. Diego pose la brosse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Diego se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Diego a pris la brosse. Il brosse avec l'adulte. Matin et soir. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Diego se rince la bouche. Il dit merci à maman. Les dents brillent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Les dents sont propres. Diego pose la brosse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Diego se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Diego a pris la brosse. Il brosse avec l'adulte. Matin et soir. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Diego se rince la bouche. Il dit merci à maman. Les dents brillent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diego prend sa brosse</t>
+          <t>La brosse jaune de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le radiateur fait tic. Raphaël prend sa brosse jaune avec papa le matin, puis avec maman le soir. Ça goûte la fraise.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, Diego se lève. Papa l'appelle. Ils vont dans la salle de bain. Diego prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Diego rit un peu. Il range la brosse. Le soir, maman l'appelle. C'est pareil. Diego prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. Matin et soir. Matin et soir. Oui, avec un adulte. Les dents sont propres. Diego pose la brosse.</t>
+          <t>Le radiateur fait tic, tic, tic. Une chaussette rouge est par terre. La bouilloire fait un nuage. Un gobelet jaune est près du lavabo. Ça sent le pain, tout loin. Le carrelage est un peu froid. Raphaël, viens. On va brosser. J'arrive, papa. Tu vois le gobelet jaune ? Oui. Comme ma brosse. En ce moment, Raphaël se lève. Ils vont dans la salle de bain. Prends ta brosse. Elle est jaune. Raphaël prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Oui. On brosse ensemble. Raphaël rit un peu. Il se rince. L'eau est fraîche. Il range la brosse. Bravo. Tu as fait du bon travail. C'est le matin. On a brossé. Avec toi. Oui. Avec un adulte. Plus tard, le soir arrive. Le radiateur fait encore tic. Raphaël, viens. C'est le soir. Ma brosse jaune. Raphaël prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec un adulte. Le matin avec papa. Le soir avec moi. Les dents sont propres. Raphaël pose la brosse. Tu as fini de brosser ? Oui, maman. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le matin, Diego se lève. Papa l'appelle. Ils vont dans la salle de bain. Diego prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Diego rit un peu. Il range la brosse. Le soir, maman l'appelle. C'est pareil. Diego prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. Matin et soir.
+          <t>narrateur|Le radiateur fait tic, tic, tic.
+narrateur|Une chaussette rouge est par terre.
+narrateur|La bouilloire fait un nuage.
+narrateur|Un gobelet jaune est près du lavabo.
+narrateur|Ça sent le pain, tout loin.
+narrateur|Le carrelage est un peu froid.
+papa|Raphaël, viens. On va brosser.
+enfant-m|J'arrive, papa.
+papa|Tu vois le gobelet jaune ?
+enfant-m|Oui. Comme ma brosse.
+narrateur|En ce moment, Raphaël se lève.
+narrateur|Ils vont dans la salle de bain.
+papa|Prends ta brosse.
+enfant-m|Elle est jaune.
+narrateur|Raphaël prend sa brosse.
+narrateur|La brosse est jaune.
+narrateur|Un adulte est avec lui.
+narrateur|C'est papa.
+narrateur|Ils se brossent les dents.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
+enfant-m|Ça goûte la fraise.
+papa|Oui. On brosse ensemble.
+narrateur|Raphaël rit un peu.
+narrateur|Il se rince.
+narrateur|L'eau est fraîche.
+narrateur|Il range la brosse.
+papa|Bravo. Tu as fait du bon travail.
+papa|C'est le matin. On a brossé.
+enfant-m|Avec toi.
+papa|Oui. Avec un adulte.
+narrateur|Plus tard, le soir arrive.
+narrateur|Le radiateur fait encore tic.
+maman|Raphaël, viens. C'est le soir.
+enfant-m|Ma brosse jaune.
+narrateur|Raphaël prend sa brosse.
+narrateur|Un adulte est avec lui.
+narrateur|C'est maman.
+narrateur|Ils brossent ensemble.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
 enfant-m|Matin et soir.
 maman|Oui, avec un adulte.
-narrateur|Les dents sont propres. Diego pose la brosse.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Le matin avec papa.
+maman|Le soir avec moi.
+narrateur|Les dents sont propres.
+narrateur|Raphaël pose la brosse.
+maman|Tu as fini de brosser ?
+enfant-m|Oui, maman.
+maman|Bravo, Raphaël.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Diego se brosse les dents. Avec quoi ?</t>
+          <t>Raphaël se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,10 +1560,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Diego se brosse les dents. Avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël se brosse les dents.
+narrateur|Avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Diego a pris la brosse. Il brosse avec l'adulte. Matin et soir. Papa et maman sont là.</t>
+          <t>Raphaël a pris la brosse. Il brosse avec l'adulte. Matin et soir. Papa et maman sont là. Tu te souviens ? Matin et soir. Oui. Avec la brosse. Bravo. C'est le bon geste. Le gobelet jaune attend encore. La chaussette rouge n'est plus par terre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,10 +1732,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Diego a pris la brosse. Il brosse avec l'adulte. Matin et soir. Papa et maman sont là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a pris la brosse.
+narrateur|Il brosse avec l'adulte.
+narrateur|Matin et soir.
+narrateur|Papa et maman sont là.
+maman|Tu te souviens ? Matin et soir.
+enfant-m|Oui. Avec la brosse.
+papa|Bravo. C'est le bon geste.
+narrateur|Le gobelet jaune attend encore.
+narrateur|La chaussette rouge n'est plus par terre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,7 +1767,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Diego se rince la bouche. Il dit merci à maman. Les dents brillent.</t>
+          <t>Raphaël se rince la bouche. L'eau est fraîche. Merci, maman. Tes dents brillent. Tu as fini ? Oui. Bravo. On va au lit. La chaussette n'est plus par terre. Le radiateur fait tic, tout doux. Ça goûte encore un peu la fraise.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,10 +1903,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Diego se rince la bouche. Il dit merci à maman. Les dents brillent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël se rince la bouche.
+narrateur|L'eau est fraîche.
+enfant-m|Merci, maman.
+maman|Tes dents brillent.
+maman|Tu as fini ?
+enfant-m|Oui.
+papa|Bravo. On va au lit.
+narrateur|La chaussette n'est plus par terre.
+narrateur|Le radiateur fait tic, tout doux.
+narrateur|Ça goûte encore un peu la fraise.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,7 +1939,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a brossé le matin. Raphaël a brossé le soir. Avec papa. Avec maman. Avec la brosse. Bravo, Raphaël. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,10 +2079,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Raphaël a brossé le matin.
+narrateur|Raphaël a brossé le soir.
+narrateur|Avec papa. Avec maman. Avec la brosse.
+maman|Bravo, Raphaël.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur fait tic, tic, tic. Une chaussette rouge est par terre. La bouilloire fait un nuage. Un gobelet jaune est près du lavabo. Ça sent le pain, tout loin. Le carrelage est un peu froid. Raphaël, viens. On va brosser. J'arrive, papa. Tu vois le gobelet jaune ? Oui. Comme ma brosse. En ce moment, Raphaël se lève. Ils vont dans la salle de bain. Prends ta brosse. Elle est jaune. Raphaël prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Oui. On brosse ensemble. Raphaël rit un peu. Il se rince. L'eau est fraîche. Il range la brosse. Bravo. Tu as fait du bon travail. C'est le matin. On a brossé. Avec toi. Oui. Avec un adulte. Plus tard, le soir arrive. Le radiateur fait encore tic. Raphaël, viens. C'est le soir. Ma brosse jaune. Raphaël prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec un adulte. Le matin avec papa. Le soir avec moi. Les dents sont propres. Raphaël pose la brosse. Tu as fini de brosser ? Oui, maman. Bravo, Raphaël.</t>
+          <t>Le radiateur fait tic, tic, tic. Une chaussette rouge est par terre. La bouilloire fait un nuage. Un gobelet jaune est près du lavabo. Ça sent le pain, tout loin. Le carrelage est un peu froid. Raphaël, viens. On va brosser. J'arrive, papa. Tu vois le gobelet jaune ? Oui. Comme ma brosse. En ce moment, Raphaël se lève. Ils vont dans la salle de bain. Prends ta brosse. Elle est jaune. Raphaël prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Oui. On brosse ensemble. Raphaël rit un peu. Il se rince. L'eau est fraîche. Il range la brosse. Le matin, on a brossé. Avec toi. Oui. Avec un adulte. Raphaël regarde le gobelet jaune. Ça goûte encore la fraise. C'est bon. Oui. Bravo. Plus tard, le soir arrive. Le radiateur fait encore tic. Raphaël, viens. C'est le soir. Ma brosse jaune. Raphaël prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec un adulte. Le matin avec papa. Le soir avec moi. Les dents sont propres. Raphaël pose la brosse. Tu as fini de brosser ? Oui, maman. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt;, Diego se lève. Papa l'appelle. Ils vont dans la salle de bain. Diego prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Diego rit un peu. Il range la brosse. Le soir, maman l'appelle. C'est pareil. Diego prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. Matin et soir. Diego dit : matin et soir. Maman dit : oui, avec un adulte. Les dents sont propres. Diego pose la brosse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le radiateur fait tic, tic, tic. Une chaussette rouge est par terre. La bouilloire fait un nuage. Un gobelet jaune est près du lavabo. Ça sent le pain, tout loin. Le carrelage est un peu froid. Raphaël, viens. On va brosser. J'arrive, papa. Tu vois le gobelet jaune ? Oui. Comme ma brosse. En ce moment, Raphaël se lève. Ils vont dans la salle de bain. Prends ta brosse. Elle est jaune. Raphaël prend sa brosse. La brosse est jaune. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. Ça goûte la fraise. Oui. On brosse ensemble. Raphaël rit un peu. Il se rince. L'eau est fraîche. Il range la brosse. Le matin, on a brossé. Avec toi. Oui. Avec un adulte. Raphaël regarde le gobelet jaune. Ça goûte encore la fraise. C'est bon. Oui. Bravo. Plus tard, le soir arrive. Le radiateur fait encore tic. Raphaël, viens. C'est le soir. Ma brosse jaune. Raphaël prend sa brosse. Un adulte est avec lui. C'est maman. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec un adulte. Le matin avec papa. Le soir avec moi. Les dents sont propres. Raphaël pose la brosse. Tu as fini de brosser ? Oui, maman. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1351,10 +1351,13 @@
 narrateur|Il se rince.
 narrateur|L'eau est fraîche.
 narrateur|Il range la brosse.
-papa|Bravo. Tu as fait du bon travail.
-papa|C'est le matin. On a brossé.
+papa|Le matin, on a brossé.
 enfant-m|Avec toi.
 papa|Oui. Avec un adulte.
+narrateur|Raphaël regarde le gobelet jaune.
+narrateur|Ça goûte encore la fraise.
+enfant-m|C'est bon.
+papa|Oui. Bravo.
 narrateur|Plus tard, le soir arrive.
 narrateur|Le radiateur fait encore tic.
 maman|Raphaël, viens. C'est le soir.
@@ -1405,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Diego se &lt;emphasis level="moderate"&gt;brosse&lt;/emphasis&gt; les dents. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1588,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a pris la brosse. Il brosse avec l'adulte. Matin et soir. Papa et maman sont là. Tu te souviens ? Matin et soir. Oui. Avec la brosse. Bravo. C'est le bon geste. Le gobelet jaune attend encore. La chaussette rouge n'est plus par terre.</t>
+          <t>Raphaël a pris la brosse. Il brosse avec l'adulte. Matin et soir. Tu te souviens ? Matin et soir. Oui. Avec la brosse. Bravo. C'est le bon geste. Le gobelet jaune attend encore. La chaussette rouge n'est plus par terre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Diego a pris la brosse. Il brosse avec l'adulte. &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt; et soir. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a pris la brosse. Il brosse avec l'adulte. Matin et soir. Tu te souviens ? Matin et soir. Oui. Avec la brosse. Bravo. C'est le bon geste. Le gobelet jaune attend encore. La chaussette rouge n'est plus par terre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1735,7 +1738,6 @@
           <t>narrateur|Raphaël a pris la brosse.
 narrateur|Il brosse avec l'adulte.
 narrateur|Matin et soir.
-narrateur|Papa et maman sont là.
 maman|Tu te souviens ? Matin et soir.
 enfant-m|Oui. Avec la brosse.
 papa|Bravo. C'est le bon geste.
@@ -1772,7 +1774,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Diego se rince la bouche. Il dit merci à maman. Les dents brillent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël se rince la bouche. L'eau est fraîche. Merci, maman. Tes dents brillent. Tu as fini ? Oui. Bravo. On va au lit. La chaussette n'est plus par terre. Le radiateur fait tic, tout doux. Ça goûte encore un peu la fraise.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a brossé le matin. Raphaël a brossé le soir. Avec papa. Avec maman. Avec la brosse. Bravo, Raphaël. L'histoire est finie.</t>
+          <t>Raphaël a brossé le matin. Raphaël a brossé le soir. Avec papa. Avec maman. Avec la brosse. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a brossé le matin. Raphaël a brossé le soir. Avec papa. Avec maman. Avec la brosse. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2082,8 +2084,7 @@
           <t>narrateur|Raphaël a brossé le matin.
 narrateur|Raphaël a brossé le soir.
 narrateur|Avec papa. Avec maman. Avec la brosse.
-maman|Bravo, Raphaël.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Raphaël.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2150,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diego, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
